--- a/master/result/07_霸道总裁：职场娇妻/07_办公室恋情_禁忌之爱.xlsx
+++ b/master/result/07_霸道总裁：职场娇妻/07_办公室恋情_禁忌之爱.xlsx
@@ -397,434 +397,549 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:D38"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>importance</v>
       </c>
       <c r="B2" t="str">
-        <v>importance</v>
+        <v>/importance/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>重要性</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>orientation</v>
       </c>
       <c r="B3" t="str">
-        <v>orientation</v>
+        <v>/orientation/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>方向</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>interior</v>
       </c>
       <c r="B4" t="str">
-        <v>interior</v>
+        <v>/interior/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>内部</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>regulation</v>
       </c>
       <c r="B5" t="str">
+        <v>/regulation/</v>
+      </c>
+      <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>规章</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>scheme</v>
+      </c>
+      <c r="B6" t="str">
+        <v>/scheme/</v>
+      </c>
+      <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>方案</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>doubt</v>
+      </c>
+      <c r="B7" t="str">
+        <v>/daʊt/</v>
+      </c>
+      <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>怀疑</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>textile</v>
+      </c>
+      <c r="B8" t="str">
+        <v>/textile/</v>
+      </c>
+      <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>纺织</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>excel</v>
+      </c>
+      <c r="B9" t="str">
+        <v>/excel/</v>
+      </c>
+      <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>擅长</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>reliance</v>
+      </c>
+      <c r="B10" t="str">
+        <v>/reliance/</v>
+      </c>
+      <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>依赖</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="B11" t="str">
+        <v>/Tuesday/</v>
+      </c>
+      <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>星期二</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>comedy</v>
+      </c>
+      <c r="B12" t="str">
+        <v>/ˈkɒmədi/</v>
+      </c>
+      <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>喜剧</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>exciting</v>
+      </c>
+      <c r="B13" t="str">
+        <v>/exciting/</v>
+      </c>
+      <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>令人兴奋</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>void</v>
+      </c>
+      <c r="B14" t="str">
+        <v>/void/</v>
+      </c>
+      <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>空虚</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>waiter</v>
+      </c>
+      <c r="B15" t="str">
+        <v>/waiter/</v>
+      </c>
+      <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>服务员</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>expand</v>
+      </c>
+      <c r="B16" t="str">
+        <v>/ɪkˈspænd/</v>
+      </c>
+      <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>扩张</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>overhear</v>
+      </c>
+      <c r="B17" t="str">
+        <v>/overhear/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>偶然听到</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>genuine</v>
+      </c>
+      <c r="B18" t="str">
+        <v>/genuine/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>真实的</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>locate</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/ləʊˈkeɪt/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>位于</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>fight</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/faɪt/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>战斗</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>sore</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/sore/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>疼痛</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
         <v>regulation</v>
       </c>
-      <c r="C5" t="str">
-        <v>规章</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>scheme</v>
-      </c>
-      <c r="C6" t="str">
-        <v>方案</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>doubt</v>
-      </c>
-      <c r="C7" t="str">
-        <v>怀疑</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>textile</v>
-      </c>
-      <c r="C8" t="str">
-        <v>纺织</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>excel</v>
-      </c>
-      <c r="C9" t="str">
-        <v>擅长</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>reliance</v>
-      </c>
-      <c r="C10" t="str">
-        <v>依赖</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Tuesday</v>
-      </c>
-      <c r="C11" t="str">
-        <v>星期二</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>comedy</v>
-      </c>
-      <c r="C12" t="str">
-        <v>喜剧</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>exciting</v>
-      </c>
-      <c r="C13" t="str">
-        <v>令人兴奋</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>void</v>
-      </c>
-      <c r="C14" t="str">
-        <v>空虚</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>waiter</v>
-      </c>
-      <c r="C15" t="str">
-        <v>服务员</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>expand</v>
-      </c>
-      <c r="C16" t="str">
-        <v>扩张</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>overhear</v>
-      </c>
-      <c r="C17" t="str">
-        <v>偶然听到</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>genuine</v>
-      </c>
-      <c r="C18" t="str">
-        <v>真实的</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>locate</v>
-      </c>
-      <c r="C19" t="str">
-        <v>位于</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>fight</v>
-      </c>
-      <c r="C20" t="str">
-        <v>战斗</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>sore</v>
-      </c>
-      <c r="C21" t="str">
-        <v>疼痛</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
       <c r="B22" t="str">
-        <v>regulation</v>
+        <v>/regulation/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>规定</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>cruel</v>
       </c>
       <c r="B23" t="str">
-        <v>cruel</v>
+        <v>/ˈkruːəl/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>残酷</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>switch</v>
       </c>
       <c r="B24" t="str">
-        <v>switch</v>
+        <v>/swɪtʃ/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>转换</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>barn</v>
       </c>
       <c r="B25" t="str">
-        <v>barn</v>
+        <v>/barn/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>谷仓</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>likewise</v>
       </c>
       <c r="B26" t="str">
-        <v>likewise</v>
+        <v>/likewise/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>同样</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>housework</v>
       </c>
       <c r="B27" t="str">
-        <v>housework</v>
+        <v>/housework/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>家务</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>exhibit</v>
       </c>
       <c r="B28" t="str">
-        <v>exhibit</v>
+        <v>/exhibit/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>展览</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>universe</v>
       </c>
       <c r="B29" t="str">
-        <v>universe</v>
+        <v>/universe/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>星空</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>innumerable</v>
       </c>
       <c r="B30" t="str">
-        <v>innumerable</v>
+        <v>/innumerable/</v>
       </c>
       <c r="C30" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>无数的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>conclude</v>
       </c>
       <c r="B31" t="str">
-        <v>conclude</v>
+        <v>/conclude/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>达成</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>barber</v>
       </c>
       <c r="B32" t="str">
-        <v>barber</v>
+        <v>/barber/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>理发店</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>princess</v>
       </c>
       <c r="B33" t="str">
-        <v>princess</v>
+        <v>/princess/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>公主</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>aboard</v>
       </c>
       <c r="B34" t="str">
-        <v>aboard</v>
+        <v>/aboard/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>在飞机上</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>brave</v>
       </c>
       <c r="B35" t="str">
-        <v>brave</v>
+        <v>/breɪv/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>面对</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>outcome</v>
       </c>
       <c r="B36" t="str">
-        <v>outcome</v>
+        <v>/outcome/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>结局</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>acceptance</v>
       </c>
       <c r="B37" t="str">
-        <v>acceptance</v>
+        <v>/acceptance/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>接纳</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>confidence</v>
       </c>
       <c r="B38" t="str">
-        <v>confidence</v>
+        <v>/ˈkɒnfɪdəns/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>信心</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
   </ignoredErrors>
 </worksheet>
 </file>